--- a/communication/research/HSF_Programme_Stories_Communication_240_Idea_Bank_Editorial_Inventory.xlsx
+++ b/communication/research/HSF_Programme_Stories_Communication_240_Idea_Bank_Editorial_Inventory.xlsx
@@ -2,9 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review Dashboard" sheetId="1" r:id="R9ba040fdce9a411c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PSC 240 Ideas" sheetId="2" r:id="Ra5b4840eb6834294"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence and Approval" sheetId="3" r:id="Rdfdc6a20a02443b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review Dashboard" sheetId="1" r:id="R7d473af4e9e444ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PSC 240 Ideas" sheetId="2" r:id="R6f85a7d7d7ab4c57"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence and Approval" sheetId="3" r:id="R5e9d5901c1ec45ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Approval History" sheetId="4" r:id="R4b965a50eeea44cc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -44,7 +45,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="7">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -66,6 +67,16 @@
         <x:fgColor rgb="FFDAEFE2"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF006B35"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEFF8F3"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -74,7 +85,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="26">
+  <x:cellXfs count="31">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -125,6 +136,11 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -370,15 +386,15 @@
         <x:v>Editorial-approved (planning only)</x:v>
       </x:c>
       <x:c r="B5" t="n">
-        <x:v>140</x:v>
+        <x:v>240</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" t="str">
-        <x:v>New proposed PSC concepts</x:v>
+        <x:v>Editorial proposed (remaining)</x:v>
       </x:c>
       <x:c r="B6" t="n">
-        <x:v>100</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -419,10 +435,10 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="C11" t="n">
-        <x:v>46</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D11" t="n">
-        <x:v>30</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -433,10 +449,10 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="C12" t="n">
-        <x:v>48</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D12" t="n">
-        <x:v>35</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -447,10 +463,10 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="C13" t="n">
-        <x:v>33</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D13" t="n">
-        <x:v>25</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -461,10 +477,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="C14" t="n">
-        <x:v>13</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D14" t="n">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -493,7 +509,7 @@
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="24" t="str">
-        <x:v>New PSC-141..240 are possible stories, not asserted real events</x:v>
+        <x:v>New PSC-141..240 approved for planning ONLY; actual events still NOT_CONFIRMED</x:v>
       </x:c>
       <x:c r="B18" s="24" t="str"/>
       <x:c r="C18" s="24" t="str"/>
@@ -6968,7 +6984,7 @@
         <x:v>HIGH: child safeguarding; no identifying learner media or family details; do not infer learning gains or programme outcomes.</x:v>
       </x:c>
       <x:c r="J142" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K142" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -7015,7 +7031,7 @@
         <x:v>HIGH: child safeguarding; no identifying learner media or family details; do not infer learning gains or programme outcomes.</x:v>
       </x:c>
       <x:c r="J143" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K143" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -7062,7 +7078,7 @@
         <x:v>HIGH: child safeguarding; no identifying learner media or family details; do not infer learning gains or programme outcomes.</x:v>
       </x:c>
       <x:c r="J144" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K144" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -7109,7 +7125,7 @@
         <x:v>HIGH: child safeguarding; no identifying learner media or family details; do not infer learning gains or programme outcomes.</x:v>
       </x:c>
       <x:c r="J145" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K145" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -7156,7 +7172,7 @@
         <x:v>HIGH: child safeguarding; no identifying learner media or family details; do not infer learning gains or programme outcomes.</x:v>
       </x:c>
       <x:c r="J146" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K146" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -7203,7 +7219,7 @@
         <x:v>HIGH: child safeguarding; no identifying learner media or family details; do not infer learning gains or programme outcomes.</x:v>
       </x:c>
       <x:c r="J147" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K147" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -7250,7 +7266,7 @@
         <x:v>HIGH: child safeguarding; no identifying learner media or family details; do not infer learning gains or programme outcomes.</x:v>
       </x:c>
       <x:c r="J148" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K148" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -7297,7 +7313,7 @@
         <x:v>HIGH: child safeguarding; no identifying learner media or family details; do not infer learning gains or programme outcomes.</x:v>
       </x:c>
       <x:c r="J149" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K149" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -7344,7 +7360,7 @@
         <x:v>HIGH: child safeguarding; no identifying learner media or family details; do not infer learning gains or programme outcomes.</x:v>
       </x:c>
       <x:c r="J150" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K150" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -7391,7 +7407,7 @@
         <x:v>HIGH: child safeguarding; no identifying learner media or family details; do not infer learning gains or programme outcomes.</x:v>
       </x:c>
       <x:c r="J151" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K151" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -7438,7 +7454,7 @@
         <x:v>HIGH: child safeguarding; no identifying learner media or family details; do not infer learning gains or programme outcomes.</x:v>
       </x:c>
       <x:c r="J152" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K152" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -7485,7 +7501,7 @@
         <x:v>HIGH: child safeguarding; no identifying learner media or family details; do not infer learning gains or programme outcomes.</x:v>
       </x:c>
       <x:c r="J153" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K153" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -7532,7 +7548,7 @@
         <x:v>HIGH: child safeguarding; no identifying learner media or family details; do not infer learning gains or programme outcomes.</x:v>
       </x:c>
       <x:c r="J154" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K154" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -7579,7 +7595,7 @@
         <x:v>HIGH: child safeguarding; no identifying learner media or family details; do not infer learning gains or programme outcomes.</x:v>
       </x:c>
       <x:c r="J155" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K155" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -7626,7 +7642,7 @@
         <x:v>HIGH: child safeguarding; no identifying learner media or family details; do not infer learning gains or programme outcomes.</x:v>
       </x:c>
       <x:c r="J156" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K156" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -7673,7 +7689,7 @@
         <x:v>HIGH: child safeguarding; no identifying learner media or family details; do not infer learning gains or programme outcomes.</x:v>
       </x:c>
       <x:c r="J157" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K157" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -7720,7 +7736,7 @@
         <x:v>HIGH: child safeguarding; no identifying learner media or family details; do not infer learning gains or programme outcomes.</x:v>
       </x:c>
       <x:c r="J158" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K158" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -7767,7 +7783,7 @@
         <x:v>HIGH: child safeguarding; no identifying learner media or family details; do not infer learning gains or programme outcomes.</x:v>
       </x:c>
       <x:c r="J159" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K159" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -7814,7 +7830,7 @@
         <x:v>HIGH: child safeguarding; no identifying learner media or family details; do not infer learning gains or programme outcomes.</x:v>
       </x:c>
       <x:c r="J160" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K160" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -7861,7 +7877,7 @@
         <x:v>HIGH: child safeguarding; no identifying learner media or family details; do not infer learning gains or programme outcomes.</x:v>
       </x:c>
       <x:c r="J161" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K161" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -7908,7 +7924,7 @@
         <x:v>HIGH: child safeguarding; no identifying learner media or family details; do not infer learning gains or programme outcomes.</x:v>
       </x:c>
       <x:c r="J162" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K162" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -7955,7 +7971,7 @@
         <x:v>HIGH: child safeguarding; no identifying learner media or family details; do not infer learning gains or programme outcomes.</x:v>
       </x:c>
       <x:c r="J163" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K163" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -8002,7 +8018,7 @@
         <x:v>HIGH: child safeguarding; no identifying learner media or family details; do not infer learning gains or programme outcomes.</x:v>
       </x:c>
       <x:c r="J164" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K164" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -8049,7 +8065,7 @@
         <x:v>HIGH: child safeguarding; no identifying learner media or family details; do not infer learning gains or programme outcomes.</x:v>
       </x:c>
       <x:c r="J165" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K165" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -8096,7 +8112,7 @@
         <x:v>HIGH: child safeguarding; no identifying learner media or family details; do not infer learning gains or programme outcomes.</x:v>
       </x:c>
       <x:c r="J166" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K166" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -8143,7 +8159,7 @@
         <x:v>HIGH: child safeguarding; no identifying learner media or family details; do not infer learning gains or programme outcomes.</x:v>
       </x:c>
       <x:c r="J167" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K167" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -8190,7 +8206,7 @@
         <x:v>HIGH: child safeguarding; no identifying learner media or family details; do not infer learning gains or programme outcomes.</x:v>
       </x:c>
       <x:c r="J168" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K168" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -8237,7 +8253,7 @@
         <x:v>HIGH: child safeguarding; no identifying learner media or family details; do not infer learning gains or programme outcomes.</x:v>
       </x:c>
       <x:c r="J169" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K169" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -8284,7 +8300,7 @@
         <x:v>HIGH: child safeguarding; no identifying learner media or family details; do not infer learning gains or programme outcomes.</x:v>
       </x:c>
       <x:c r="J170" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K170" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -8331,7 +8347,7 @@
         <x:v>HIGH: child safeguarding; no identifying learner media or family details; do not infer learning gains or programme outcomes.</x:v>
       </x:c>
       <x:c r="J171" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K171" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -8378,7 +8394,7 @@
         <x:v>HIGH: patient privacy, licensed clinical/medical review and informed permissions; no identifying records or medical outcome claims.</x:v>
       </x:c>
       <x:c r="J172" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K172" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -8425,7 +8441,7 @@
         <x:v>HIGH: patient privacy, licensed clinical/medical review and informed permissions; no identifying records or medical outcome claims.</x:v>
       </x:c>
       <x:c r="J173" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K173" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -8472,7 +8488,7 @@
         <x:v>HIGH: patient privacy, licensed clinical/medical review and informed permissions; no identifying records or medical outcome claims.</x:v>
       </x:c>
       <x:c r="J174" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K174" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -8519,7 +8535,7 @@
         <x:v>HIGH: patient privacy, licensed clinical/medical review and informed permissions; no identifying records or medical outcome claims.</x:v>
       </x:c>
       <x:c r="J175" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K175" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -8566,7 +8582,7 @@
         <x:v>HIGH: patient privacy, licensed clinical/medical review and informed permissions; no identifying records or medical outcome claims.</x:v>
       </x:c>
       <x:c r="J176" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K176" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -8613,7 +8629,7 @@
         <x:v>HIGH: patient privacy, licensed clinical/medical review and informed permissions; no identifying records or medical outcome claims.</x:v>
       </x:c>
       <x:c r="J177" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K177" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -8660,7 +8676,7 @@
         <x:v>HIGH: patient privacy, licensed clinical/medical review and informed permissions; no identifying records or medical outcome claims.</x:v>
       </x:c>
       <x:c r="J178" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K178" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -8707,7 +8723,7 @@
         <x:v>HIGH: patient privacy, licensed clinical/medical review and informed permissions; no identifying records or medical outcome claims.</x:v>
       </x:c>
       <x:c r="J179" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K179" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -8754,7 +8770,7 @@
         <x:v>HIGH: patient privacy, licensed clinical/medical review and informed permissions; no identifying records or medical outcome claims.</x:v>
       </x:c>
       <x:c r="J180" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K180" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -8801,7 +8817,7 @@
         <x:v>HIGH: patient privacy, licensed clinical/medical review and informed permissions; no identifying records or medical outcome claims.</x:v>
       </x:c>
       <x:c r="J181" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K181" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -8848,7 +8864,7 @@
         <x:v>HIGH: patient privacy, licensed clinical/medical review and informed permissions; no identifying records or medical outcome claims.</x:v>
       </x:c>
       <x:c r="J182" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K182" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -8895,7 +8911,7 @@
         <x:v>HIGH: patient privacy, licensed clinical/medical review and informed permissions; no identifying records or medical outcome claims.</x:v>
       </x:c>
       <x:c r="J183" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K183" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -8942,7 +8958,7 @@
         <x:v>HIGH: patient privacy, licensed clinical/medical review and informed permissions; no identifying records or medical outcome claims.</x:v>
       </x:c>
       <x:c r="J184" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K184" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -8989,7 +9005,7 @@
         <x:v>HIGH: patient privacy, licensed clinical/medical review and informed permissions; no identifying records or medical outcome claims.</x:v>
       </x:c>
       <x:c r="J185" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K185" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -9036,7 +9052,7 @@
         <x:v>HIGH: patient privacy, licensed clinical/medical review and informed permissions; no identifying records or medical outcome claims.</x:v>
       </x:c>
       <x:c r="J186" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K186" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -9083,7 +9099,7 @@
         <x:v>HIGH: patient privacy, licensed clinical/medical review and informed permissions; no identifying records or medical outcome claims.</x:v>
       </x:c>
       <x:c r="J187" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K187" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -9130,7 +9146,7 @@
         <x:v>HIGH: patient privacy, licensed clinical/medical review and informed permissions; no identifying records or medical outcome claims.</x:v>
       </x:c>
       <x:c r="J188" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K188" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -9177,7 +9193,7 @@
         <x:v>HIGH: patient privacy, licensed clinical/medical review and informed permissions; no identifying records or medical outcome claims.</x:v>
       </x:c>
       <x:c r="J189" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K189" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -9224,7 +9240,7 @@
         <x:v>HIGH: patient privacy, licensed clinical/medical review and informed permissions; no identifying records or medical outcome claims.</x:v>
       </x:c>
       <x:c r="J190" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K190" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -9271,7 +9287,7 @@
         <x:v>HIGH: patient privacy, licensed clinical/medical review and informed permissions; no identifying records or medical outcome claims.</x:v>
       </x:c>
       <x:c r="J191" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K191" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -9318,7 +9334,7 @@
         <x:v>HIGH: patient privacy, licensed clinical/medical review and informed permissions; no identifying records or medical outcome claims.</x:v>
       </x:c>
       <x:c r="J192" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K192" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -9365,7 +9381,7 @@
         <x:v>HIGH: patient privacy, licensed clinical/medical review and informed permissions; no identifying records or medical outcome claims.</x:v>
       </x:c>
       <x:c r="J193" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K193" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -9412,7 +9428,7 @@
         <x:v>HIGH: patient privacy, licensed clinical/medical review and informed permissions; no identifying records or medical outcome claims.</x:v>
       </x:c>
       <x:c r="J194" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K194" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -9459,7 +9475,7 @@
         <x:v>HIGH: patient privacy, licensed clinical/medical review and informed permissions; no identifying records or medical outcome claims.</x:v>
       </x:c>
       <x:c r="J195" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K195" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -9506,7 +9522,7 @@
         <x:v>HIGH: patient privacy, licensed clinical/medical review and informed permissions; no identifying records or medical outcome claims.</x:v>
       </x:c>
       <x:c r="J196" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K196" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -9553,7 +9569,7 @@
         <x:v>HIGH: patient privacy, licensed clinical/medical review and informed permissions; no identifying records or medical outcome claims.</x:v>
       </x:c>
       <x:c r="J197" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K197" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -9600,7 +9616,7 @@
         <x:v>HIGH: patient privacy, licensed clinical/medical review and informed permissions; no identifying records or medical outcome claims.</x:v>
       </x:c>
       <x:c r="J198" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K198" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -9647,7 +9663,7 @@
         <x:v>HIGH: patient privacy, licensed clinical/medical review and informed permissions; no identifying records or medical outcome claims.</x:v>
       </x:c>
       <x:c r="J199" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K199" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -9694,7 +9710,7 @@
         <x:v>HIGH: patient privacy, licensed clinical/medical review and informed permissions; no identifying records or medical outcome claims.</x:v>
       </x:c>
       <x:c r="J200" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K200" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -9741,7 +9757,7 @@
         <x:v>HIGH: patient privacy, licensed clinical/medical review and informed permissions; no identifying records or medical outcome claims.</x:v>
       </x:c>
       <x:c r="J201" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K201" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -9788,7 +9804,7 @@
         <x:v>HIGH: patient privacy, licensed clinical/medical review and informed permissions; no identifying records or medical outcome claims.</x:v>
       </x:c>
       <x:c r="J202" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K202" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -9835,7 +9851,7 @@
         <x:v>HIGH: patient privacy, licensed clinical/medical review and informed permissions; no identifying records or medical outcome claims.</x:v>
       </x:c>
       <x:c r="J203" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K203" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -9882,7 +9898,7 @@
         <x:v>HIGH: patient privacy, licensed clinical/medical review and informed permissions; no identifying records or medical outcome claims.</x:v>
       </x:c>
       <x:c r="J204" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K204" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -9929,7 +9945,7 @@
         <x:v>HIGH: patient privacy, licensed clinical/medical review and informed permissions; no identifying records or medical outcome claims.</x:v>
       </x:c>
       <x:c r="J205" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K205" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -9976,7 +9992,7 @@
         <x:v>HIGH: patient privacy, licensed clinical/medical review and informed permissions; no identifying records or medical outcome claims.</x:v>
       </x:c>
       <x:c r="J206" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K206" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -10023,7 +10039,7 @@
         <x:v>MODERATE/HIGH: preserve informed participation, community dignity and accurate environmental attribution; technical review for science or safety.</x:v>
       </x:c>
       <x:c r="J207" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K207" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -10070,7 +10086,7 @@
         <x:v>MODERATE/HIGH: preserve informed participation, community dignity and accurate environmental attribution; technical review for science or safety.</x:v>
       </x:c>
       <x:c r="J208" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K208" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -10117,7 +10133,7 @@
         <x:v>MODERATE/HIGH: preserve informed participation, community dignity and accurate environmental attribution; technical review for science or safety.</x:v>
       </x:c>
       <x:c r="J209" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K209" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -10164,7 +10180,7 @@
         <x:v>MODERATE/HIGH: preserve informed participation, community dignity and accurate environmental attribution; technical review for science or safety.</x:v>
       </x:c>
       <x:c r="J210" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K210" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -10211,7 +10227,7 @@
         <x:v>MODERATE/HIGH: preserve informed participation, community dignity and accurate environmental attribution; technical review for science or safety.</x:v>
       </x:c>
       <x:c r="J211" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K211" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -10258,7 +10274,7 @@
         <x:v>MODERATE/HIGH: preserve informed participation, community dignity and accurate environmental attribution; technical review for science or safety.</x:v>
       </x:c>
       <x:c r="J212" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K212" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -10305,7 +10321,7 @@
         <x:v>MODERATE/HIGH: preserve informed participation, community dignity and accurate environmental attribution; technical review for science or safety.</x:v>
       </x:c>
       <x:c r="J213" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K213" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -10352,7 +10368,7 @@
         <x:v>MODERATE/HIGH: preserve informed participation, community dignity and accurate environmental attribution; technical review for science or safety.</x:v>
       </x:c>
       <x:c r="J214" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K214" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -10399,7 +10415,7 @@
         <x:v>MODERATE/HIGH: preserve informed participation, community dignity and accurate environmental attribution; technical review for science or safety.</x:v>
       </x:c>
       <x:c r="J215" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K215" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -10446,7 +10462,7 @@
         <x:v>MODERATE/HIGH: preserve informed participation, community dignity and accurate environmental attribution; technical review for science or safety.</x:v>
       </x:c>
       <x:c r="J216" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K216" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -10493,7 +10509,7 @@
         <x:v>MODERATE/HIGH: preserve informed participation, community dignity and accurate environmental attribution; technical review for science or safety.</x:v>
       </x:c>
       <x:c r="J217" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K217" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -10540,7 +10556,7 @@
         <x:v>MODERATE/HIGH: preserve informed participation, community dignity and accurate environmental attribution; technical review for science or safety.</x:v>
       </x:c>
       <x:c r="J218" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K218" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -10587,7 +10603,7 @@
         <x:v>MODERATE/HIGH: preserve informed participation, community dignity and accurate environmental attribution; technical review for science or safety.</x:v>
       </x:c>
       <x:c r="J219" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K219" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -10634,7 +10650,7 @@
         <x:v>MODERATE/HIGH: preserve informed participation, community dignity and accurate environmental attribution; technical review for science or safety.</x:v>
       </x:c>
       <x:c r="J220" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K220" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -10681,7 +10697,7 @@
         <x:v>MODERATE/HIGH: preserve informed participation, community dignity and accurate environmental attribution; technical review for science or safety.</x:v>
       </x:c>
       <x:c r="J221" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K221" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -10728,7 +10744,7 @@
         <x:v>MODERATE/HIGH: preserve informed participation, community dignity and accurate environmental attribution; technical review for science or safety.</x:v>
       </x:c>
       <x:c r="J222" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K222" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -10775,7 +10791,7 @@
         <x:v>MODERATE/HIGH: preserve informed participation, community dignity and accurate environmental attribution; technical review for science or safety.</x:v>
       </x:c>
       <x:c r="J223" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K223" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -10822,7 +10838,7 @@
         <x:v>MODERATE/HIGH: preserve informed participation, community dignity and accurate environmental attribution; technical review for science or safety.</x:v>
       </x:c>
       <x:c r="J224" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K224" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -10869,7 +10885,7 @@
         <x:v>MODERATE/HIGH: preserve informed participation, community dignity and accurate environmental attribution; technical review for science or safety.</x:v>
       </x:c>
       <x:c r="J225" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K225" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -10916,7 +10932,7 @@
         <x:v>MODERATE/HIGH: preserve informed participation, community dignity and accurate environmental attribution; technical review for science or safety.</x:v>
       </x:c>
       <x:c r="J226" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K226" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -10963,7 +10979,7 @@
         <x:v>MODERATE/HIGH: preserve informed participation, community dignity and accurate environmental attribution; technical review for science or safety.</x:v>
       </x:c>
       <x:c r="J227" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K227" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -11010,7 +11026,7 @@
         <x:v>MODERATE/HIGH: preserve informed participation, community dignity and accurate environmental attribution; technical review for science or safety.</x:v>
       </x:c>
       <x:c r="J228" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K228" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -11057,7 +11073,7 @@
         <x:v>MODERATE/HIGH: preserve informed participation, community dignity and accurate environmental attribution; technical review for science or safety.</x:v>
       </x:c>
       <x:c r="J229" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K229" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -11104,7 +11120,7 @@
         <x:v>MODERATE/HIGH: preserve informed participation, community dignity and accurate environmental attribution; technical review for science or safety.</x:v>
       </x:c>
       <x:c r="J230" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K230" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -11151,7 +11167,7 @@
         <x:v>MODERATE/HIGH: preserve informed participation, community dignity and accurate environmental attribution; technical review for science or safety.</x:v>
       </x:c>
       <x:c r="J231" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K231" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -11198,7 +11214,7 @@
         <x:v>HIGH where applicable: respect consent, governance and confidential institutional data; publish no private records or unapproved commitments.</x:v>
       </x:c>
       <x:c r="J232" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K232" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -11245,7 +11261,7 @@
         <x:v>HIGH where applicable: respect consent, governance and confidential institutional data; publish no private records or unapproved commitments.</x:v>
       </x:c>
       <x:c r="J233" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K233" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -11292,7 +11308,7 @@
         <x:v>HIGH where applicable: respect consent, governance and confidential institutional data; publish no private records or unapproved commitments.</x:v>
       </x:c>
       <x:c r="J234" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K234" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -11339,7 +11355,7 @@
         <x:v>HIGH where applicable: respect consent, governance and confidential institutional data; publish no private records or unapproved commitments.</x:v>
       </x:c>
       <x:c r="J235" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K235" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -11386,7 +11402,7 @@
         <x:v>HIGH where applicable: respect consent, governance and confidential institutional data; publish no private records or unapproved commitments.</x:v>
       </x:c>
       <x:c r="J236" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K236" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -11433,7 +11449,7 @@
         <x:v>HIGH where applicable: respect consent, governance and confidential institutional data; publish no private records or unapproved commitments.</x:v>
       </x:c>
       <x:c r="J237" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K237" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -11480,7 +11496,7 @@
         <x:v>HIGH where applicable: respect consent, governance and confidential institutional data; publish no private records or unapproved commitments.</x:v>
       </x:c>
       <x:c r="J238" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K238" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -11527,7 +11543,7 @@
         <x:v>HIGH where applicable: respect consent, governance and confidential institutional data; publish no private records or unapproved commitments.</x:v>
       </x:c>
       <x:c r="J239" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K239" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -11574,7 +11590,7 @@
         <x:v>HIGH where applicable: respect consent, governance and confidential institutional data; publish no private records or unapproved commitments.</x:v>
       </x:c>
       <x:c r="J240" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K240" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -11621,7 +11637,7 @@
         <x:v>HIGH where applicable: respect consent, governance and confidential institutional data; publish no private records or unapproved commitments.</x:v>
       </x:c>
       <x:c r="J241" s="14" t="str">
-        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="K241" s="12" t="str">
         <x:v>NOT_VERIFIED</x:v>
@@ -11678,7 +11694,7 @@
         <x:v>Reviewer</x:v>
       </x:c>
       <x:c r="D1" s="3" t="str">
-        <x:v>Status at proposal stage</x:v>
+        <x:v>Status after editorial approval</x:v>
       </x:c>
       <x:c r="E1" s="3" t="str">
         <x:v>Owner / approval ref</x:v>
@@ -11770,11 +11786,11 @@
         <x:v>HSF Communication / management</x:v>
       </x:c>
       <x:c r="D6" s="24" t="str">
-        <x:v>PROPOSED</x:v>
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
       </x:c>
       <x:c r="E6" s="24" t="str"/>
       <x:c r="F6" s="24" t="str">
-        <x:v>New 100 ideas not approved for editorial planning</x:v>
+        <x:v>200 newly reviewed KDI/PSC ideas approved for editorial planning. No confirmation of field occurrence or factual/publication approval.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="44" customHeight="1">
@@ -11793,6 +11809,81 @@
       <x:c r="E7" s="24" t="str"/>
       <x:c r="F7" s="24" t="str">
         <x:v>Approval of an idea alone does not authorize publication</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="78" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="27" customHeight="1">
+      <x:c r="A1" s="28" t="str">
+        <x:v>PSC 100-IDEA APPROVAL TRANSITION</x:v>
+      </x:c>
+      <x:c r="B1" s="28"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="30" t="str">
+        <x:v>Approval scope</x:v>
+      </x:c>
+      <x:c r="B2" s="24" t="str">
+        <x:v>Editorial planning ONLY</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="30" t="str">
+        <x:v>Idea IDs</x:v>
+      </x:c>
+      <x:c r="B3" s="24" t="str">
+        <x:v>PSC-141 through PSC-240</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="30" t="str">
+        <x:v>Prior status</x:v>
+      </x:c>
+      <x:c r="B4" s="24" t="str">
+        <x:v>EDITORIAL_IDEA_PROPOSED</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="30" t="str">
+        <x:v>Current status</x:v>
+      </x:c>
+      <x:c r="B5" s="24" t="str">
+        <x:v>EDITORIAL_IDEA_APPROVED</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="30" t="str">
+        <x:v>Story occurrence</x:v>
+      </x:c>
+      <x:c r="B6" s="24" t="str">
+        <x:v>NOT_CONFIRMED; no authentic event asserted</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="30" t="str">
+        <x:v>Review record</x:v>
+      </x:c>
+      <x:c r="B7" s="24" t="str">
+        <x:v>governance/EDITORIAL_APPROVAL_TRANSITION_v1.10.1.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="30" t="str">
+        <x:v>Publication status</x:v>
+      </x:c>
+      <x:c r="B8" s="24" t="str">
+        <x:v>NOT_APPROVED — field source, consent, technical, safeguarding and final output approvals required</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
